--- a/Data/FlightPlan/FPL_12AUG26.xlsx
+++ b/Data/FlightPlan/FPL_12AUG26.xlsx
@@ -98,6 +98,9 @@
     <t>07:35</t>
   </si>
   <si>
+    <t>07:30</t>
+  </si>
+  <si>
     <t>08:45</t>
   </si>
   <si>
@@ -125,9 +128,6 @@
     <t>08:25</t>
   </si>
   <si>
-    <t>07:30</t>
-  </si>
-  <si>
     <t>10:55</t>
   </si>
   <si>
@@ -617,6 +617,12 @@
     <t>13:35</t>
   </si>
   <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
     <t>22:00</t>
   </si>
   <si>
@@ -707,9 +713,6 @@
     <t>CZX</t>
   </si>
   <si>
-    <t>14:15</t>
-  </si>
-  <si>
     <t>23:10</t>
   </si>
   <si>
@@ -1265,7 +1268,7 @@
     <t>Total Record(s): 412</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Aug 12, 2026 01:16</t>
+    <t xml:space="preserve">Generated on  Aug 12, 2026 03:11</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -1959,7 +1962,9 @@
       </c>
       <c r="K11" s="7"/>
       <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
+      <c t="s" r="M11" s="7">
+        <v>29</v>
+      </c>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c t="s" r="A12" s="6">
@@ -1985,10 +1990,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I12" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c t="s" r="J12" s="7">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K12" s="7"/>
       <c r="L12" s="7"/>
@@ -2018,10 +2023,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I13" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c t="s" r="J13" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K13" s="7"/>
       <c r="L13" s="7"/>
@@ -2051,10 +2056,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I14" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="J14" s="7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K14" s="7"/>
       <c r="L14" s="7"/>
@@ -2087,7 +2092,7 @@
       </c>
       <c r="D16" s="7"/>
       <c t="s" r="E16" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F16" s="7">
         <v>321</v>
@@ -2099,13 +2104,13 @@
         <v>26</v>
       </c>
       <c t="s" r="I16" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="J16" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="K16" s="7">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="L16" s="7"/>
       <c t="s" r="M16" s="7">
@@ -2124,7 +2129,7 @@
       </c>
       <c r="D17" s="7"/>
       <c t="s" r="E17" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F17" s="7">
         <v>321</v>
@@ -2161,7 +2166,7 @@
       </c>
       <c r="D18" s="7"/>
       <c t="s" r="E18" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F18" s="7">
         <v>321</v>
@@ -2194,7 +2199,7 @@
       </c>
       <c r="D19" s="7"/>
       <c t="s" r="E19" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F19" s="7">
         <v>321</v>
@@ -2227,7 +2232,7 @@
       </c>
       <c r="D20" s="7"/>
       <c t="s" r="E20" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F20" s="7">
         <v>321</v>
@@ -2260,7 +2265,7 @@
       </c>
       <c r="D21" s="7"/>
       <c t="s" r="E21" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F21" s="7">
         <v>321</v>
@@ -2293,7 +2298,7 @@
       </c>
       <c r="D22" s="7"/>
       <c t="s" r="E22" s="7">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F22" s="7">
         <v>321</v>
@@ -2386,7 +2391,7 @@
         <v>63</v>
       </c>
       <c t="s" r="I25" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c t="s" r="J25" s="7">
         <v>64</v>
@@ -2569,7 +2574,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -3370,7 +3375,7 @@
         <v>120</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3993,9 +3998,13 @@
       <c t="s" r="J79" s="7">
         <v>151</v>
       </c>
-      <c r="K79" s="7"/>
+      <c t="s" r="K79" s="7">
+        <v>24</v>
+      </c>
       <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
+      <c t="s" r="M79" s="7">
+        <v>72</v>
+      </c>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c t="s" r="A80" s="6">
@@ -4026,9 +4035,13 @@
       <c t="s" r="J80" s="7">
         <v>98</v>
       </c>
-      <c r="K80" s="7"/>
+      <c t="s" r="K80" s="7">
+        <v>84</v>
+      </c>
       <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
+      <c t="s" r="M80" s="7">
+        <v>99</v>
+      </c>
     </row>
     <row r="81" ht="14.25" customHeight="1">
       <c t="s" r="A81" s="6">
@@ -4267,7 +4280,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c t="s" r="J88" s="7">
         <v>163</v>
@@ -4546,7 +4559,7 @@
         <v>176</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
@@ -4723,7 +4736,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c t="s" r="J104" s="7">
         <v>41</v>
@@ -5268,9 +5281,13 @@
       <c t="s" r="J122" s="7">
         <v>201</v>
       </c>
-      <c r="K122" s="7"/>
+      <c t="s" r="K122" s="7">
+        <v>202</v>
+      </c>
       <c r="L122" s="7"/>
-      <c r="M122" s="7"/>
+      <c t="s" r="M122" s="7">
+        <v>203</v>
+      </c>
     </row>
     <row r="123" ht="14.25" customHeight="1">
       <c t="s" r="A123" s="6">
@@ -5296,10 +5313,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
@@ -5332,7 +5349,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5347,7 +5364,7 @@
         <v>73</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5365,7 +5382,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5398,7 +5415,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5407,10 +5424,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>154</v>
@@ -5431,13 +5448,13 @@
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G128" s="8">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="H128" s="8">
         <v>60</v>
@@ -5464,7 +5481,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5476,10 +5493,10 @@
         <v>149</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J129" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
@@ -5497,7 +5514,7 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
@@ -5530,7 +5547,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5545,7 +5562,7 @@
         <v>180</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5563,7 +5580,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5575,10 +5592,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -5611,7 +5628,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5623,7 +5640,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c t="s" r="J134" s="7">
         <v>98</v>
@@ -5644,7 +5661,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5656,10 +5673,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5677,7 +5694,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5692,7 +5709,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5710,7 +5727,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5725,7 +5742,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5743,7 +5760,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5752,10 +5769,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>93</v>
@@ -5776,13 +5793,13 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>60</v>
@@ -5824,7 +5841,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -5836,10 +5853,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
@@ -5857,7 +5874,7 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
@@ -5869,7 +5886,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c t="s" r="J142" s="7">
         <v>98</v>
@@ -5890,7 +5907,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -5905,7 +5922,7 @@
         <v>99</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5923,7 +5940,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5935,7 +5952,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J144" s="7">
         <v>100</v>
@@ -5956,7 +5973,7 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
@@ -5971,7 +5988,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -5989,7 +6006,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6022,7 +6039,7 @@
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6055,7 +6072,7 @@
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6067,10 +6084,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6103,7 +6120,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6115,10 +6132,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
@@ -6136,7 +6153,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6145,10 +6162,10 @@
         <v>82</v>
       </c>
       <c t="s" r="H151" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="I151" s="7">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c t="s" r="J151" s="7">
         <v>65</v>
@@ -6169,13 +6186,13 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c t="s" r="H152" s="8">
         <v>82</v>
@@ -6184,7 +6201,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6202,7 +6219,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6214,7 +6231,7 @@
         <v>157</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>40</v>
@@ -6250,7 +6267,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6262,7 +6279,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c t="s" r="J155" s="7">
         <v>98</v>
@@ -6283,7 +6300,7 @@
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
@@ -6298,7 +6315,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K156" s="7"/>
       <c r="L156" s="7"/>
@@ -6316,7 +6333,7 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
@@ -6331,7 +6348,7 @@
         <v>180</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K157" s="7"/>
       <c r="L157" s="7"/>
@@ -6364,13 +6381,13 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>60</v>
@@ -6379,7 +6396,7 @@
         <v>87</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6397,7 +6414,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6430,7 +6447,7 @@
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
@@ -6442,10 +6459,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I161" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
@@ -6463,7 +6480,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6472,13 +6489,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c t="s" r="J162" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
@@ -6511,7 +6528,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6544,7 +6561,7 @@
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
@@ -6559,7 +6576,7 @@
         <v>147</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6577,7 +6594,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6592,7 +6609,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6610,7 +6627,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6622,10 +6639,10 @@
         <v>157</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6658,7 +6675,7 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
@@ -6673,14 +6690,14 @@
         <v>158</v>
       </c>
       <c t="s" r="J169" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="K169" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="L169" s="7"/>
       <c t="s" r="M169" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="170" ht="15" customHeight="1">
@@ -6695,7 +6712,7 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6728,7 +6745,7 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
@@ -6761,7 +6778,7 @@
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
@@ -6809,7 +6826,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -6842,7 +6859,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -6857,7 +6874,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
@@ -6875,7 +6892,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6887,10 +6904,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -6908,7 +6925,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -6920,10 +6937,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -6956,7 +6973,7 @@
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
@@ -6968,7 +6985,7 @@
         <v>165</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J179" s="7">
         <v>74</v>
@@ -6989,7 +7006,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7022,7 +7039,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7070,7 +7087,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7082,7 +7099,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c t="s" r="J183" s="7">
         <v>146</v>
@@ -7103,7 +7120,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7112,13 +7129,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I184" s="7">
         <v>160</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7136,19 +7153,19 @@
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F185" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G185" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H185" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I185" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c t="s" r="J185" s="7">
         <v>65</v>
@@ -7169,7 +7186,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7178,13 +7195,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="K186" s="7"/>
       <c r="L186" s="7"/>
@@ -7202,13 +7219,13 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>17</v>
@@ -7217,7 +7234,7 @@
         <v>94</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="K187" s="7"/>
       <c r="L187" s="7"/>
@@ -7250,7 +7267,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7262,7 +7279,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c t="s" r="J189" s="7">
         <v>201</v>
@@ -7283,7 +7300,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7292,13 +7309,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H190" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I190" s="7">
         <v>152</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7316,13 +7333,13 @@
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H191" s="8">
         <v>60</v>
@@ -7364,7 +7381,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7376,7 +7393,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>98</v>
@@ -7397,7 +7414,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7409,10 +7426,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7430,7 +7447,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7445,7 +7462,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7463,7 +7480,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7475,10 +7492,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7496,7 +7513,7 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
@@ -7529,7 +7546,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7541,7 +7558,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>128</v>
@@ -7577,7 +7594,7 @@
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
@@ -7586,13 +7603,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7610,19 +7627,19 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c t="s" r="J201" s="7">
         <v>61</v>
@@ -7643,7 +7660,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -7655,10 +7672,10 @@
         <v>86</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7676,7 +7693,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -7688,10 +7705,10 @@
         <v>119</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7709,7 +7726,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -7742,7 +7759,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -7754,10 +7771,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7775,7 +7792,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -7787,7 +7804,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>83</v>
@@ -7823,7 +7840,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -7838,7 +7855,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
@@ -7856,7 +7873,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -7868,10 +7885,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
@@ -7889,7 +7906,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -7901,10 +7918,10 @@
         <v>119</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7922,7 +7939,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -7934,7 +7951,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c t="s" r="J211" s="7">
         <v>123</v>
@@ -7955,7 +7972,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -7964,13 +7981,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>114</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -7988,22 +8005,22 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8021,7 +8038,7 @@
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F214" s="7">
         <v>321</v>
@@ -8033,10 +8050,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I214" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J214" s="7">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8069,7 +8086,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8102,7 +8119,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8114,10 +8131,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8135,7 +8152,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8150,7 +8167,7 @@
         <v>139</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8168,7 +8185,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8212,11 +8229,11 @@
         <v>21</v>
       </c>
       <c t="s" r="C221" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
@@ -8225,10 +8242,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J221" s="7">
         <v>24</v>
@@ -8264,7 +8281,7 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
@@ -8279,7 +8296,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8297,7 +8314,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8306,13 +8323,13 @@
         <v>86</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8330,13 +8347,13 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H225" s="8">
         <v>86</v>
@@ -8345,7 +8362,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8363,7 +8380,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8375,7 +8392,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>116</v>
@@ -8396,7 +8413,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8408,7 +8425,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J227" s="7">
         <v>192</v>
@@ -8444,7 +8461,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8459,7 +8476,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8477,7 +8494,7 @@
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
@@ -8492,7 +8509,7 @@
         <v>69</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8510,7 +8527,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8522,7 +8539,7 @@
         <v>149</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J231" s="7">
         <v>42</v>
@@ -8543,7 +8560,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8555,7 +8572,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c t="s" r="J232" s="7">
         <v>189</v>
@@ -8576,7 +8593,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8591,7 +8608,7 @@
         <v>199</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8609,7 +8626,7 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
@@ -8621,7 +8638,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J234" s="7">
         <v>155</v>
@@ -8642,7 +8659,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -8675,7 +8692,7 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
@@ -8687,7 +8704,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J236" s="7">
         <v>51</v>
@@ -8708,7 +8725,7 @@
       </c>
       <c r="D237" s="7"/>
       <c t="s" r="E237" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F237" s="7">
         <v>321</v>
@@ -8723,7 +8740,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8741,7 +8758,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -8789,7 +8806,7 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
@@ -8801,10 +8818,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -8822,7 +8839,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -8831,10 +8848,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H241" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>152</v>
@@ -8855,22 +8872,22 @@
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8888,7 +8905,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8897,7 +8914,7 @@
         <v>49</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="I243" s="7">
         <v>168</v>
@@ -8921,22 +8938,22 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G244" s="8">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c t="s" r="H244" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I244" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J244" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -8954,7 +8971,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -8966,7 +8983,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>24</v>
@@ -9002,7 +9019,7 @@
       </c>
       <c r="D247" s="7"/>
       <c t="s" r="E247" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F247" s="7">
         <v>321</v>
@@ -9014,7 +9031,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I247" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="J247" s="7">
         <v>97</v>
@@ -9035,7 +9052,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9047,10 +9064,10 @@
         <v>119</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
@@ -9068,7 +9085,7 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
@@ -9080,7 +9097,7 @@
         <v>44</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>159</v>
@@ -9101,7 +9118,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9113,7 +9130,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>133</v>
@@ -9134,7 +9151,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9149,7 +9166,7 @@
         <v>177</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9167,7 +9184,7 @@
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
@@ -9182,7 +9199,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
@@ -9200,7 +9217,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9248,7 +9265,7 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
@@ -9260,10 +9277,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
@@ -9281,7 +9298,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9293,7 +9310,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c t="s" r="J256" s="7">
         <v>98</v>
@@ -9314,7 +9331,7 @@
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
@@ -9347,7 +9364,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9359,7 +9376,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>74</v>
@@ -9380,7 +9397,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9413,7 +9430,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9425,10 +9442,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I260" s="7">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9446,7 +9463,7 @@
       </c>
       <c r="D261" s="7"/>
       <c t="s" r="E261" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F261" s="7">
         <v>321</v>
@@ -9458,7 +9475,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I261" s="7">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c t="s" r="J261" s="7">
         <v>168</v>
@@ -9479,7 +9496,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9512,7 +9529,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9524,10 +9541,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9545,7 +9562,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9560,7 +9577,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9593,7 +9610,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9605,10 +9622,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9626,7 +9643,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9659,7 +9676,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -9692,7 +9709,7 @@
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F269" s="7">
         <v>321</v>
@@ -9740,7 +9757,7 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
@@ -9752,10 +9769,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J271" s="7">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9773,7 +9790,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -9785,7 +9802,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c t="s" r="J272" s="7">
         <v>121</v>
@@ -9806,7 +9823,7 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
@@ -9821,7 +9838,7 @@
         <v>39</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -9839,7 +9856,7 @@
       </c>
       <c r="D274" s="7"/>
       <c t="s" r="E274" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F274" s="7">
         <v>321</v>
@@ -9854,7 +9871,7 @@
         <v>122</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9872,7 +9889,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -9905,7 +9922,7 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
@@ -9917,7 +9934,7 @@
         <v>157</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>173</v>
@@ -9953,7 +9970,7 @@
       </c>
       <c r="D278" s="7"/>
       <c t="s" r="E278" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F278" s="7">
         <v>321</v>
@@ -9962,10 +9979,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H278" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c t="s" r="J278" s="7">
         <v>18</v>
@@ -9986,13 +10003,13 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F279" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G279" s="8">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c t="s" r="H279" s="8">
         <v>17</v>
@@ -10019,7 +10036,7 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F280" s="7">
         <v>321</v>
@@ -10028,13 +10045,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H280" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="I280" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
@@ -10052,19 +10069,19 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F281" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G281" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H281" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>51</v>
@@ -10100,7 +10117,7 @@
       </c>
       <c r="D283" s="7"/>
       <c t="s" r="E283" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F283" s="7">
         <v>321</v>
@@ -10109,13 +10126,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H283" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I283" s="7">
         <v>173</v>
       </c>
       <c t="s" r="J283" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K283" s="7"/>
       <c r="L283" s="7"/>
@@ -10133,19 +10150,19 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G284" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H284" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>160</v>
@@ -10166,7 +10183,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10178,17 +10195,17 @@
         <v>17</v>
       </c>
       <c t="s" r="I285" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="K285" s="7">
         <v>180</v>
       </c>
       <c r="L285" s="7"/>
       <c t="s" r="M285" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="286" ht="14.25" customHeight="1">
@@ -10218,7 +10235,7 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
@@ -10230,7 +10247,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="J287" s="7">
         <v>112</v>
@@ -10251,7 +10268,7 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
@@ -10260,10 +10277,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H288" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J288" s="7">
         <v>199</v>
@@ -10284,22 +10301,22 @@
       </c>
       <c r="D289" s="7"/>
       <c t="s" r="E289" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F289" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G289" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H289" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I289" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10317,7 +10334,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F290" s="7">
         <v>321</v>
@@ -10326,10 +10343,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>84</v>
@@ -10365,7 +10382,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F292" s="7">
         <v>321</v>
@@ -10377,7 +10394,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>173</v>
@@ -10398,7 +10415,7 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F293" s="7">
         <v>321</v>
@@ -10413,7 +10430,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10431,7 +10448,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F294" s="7">
         <v>321</v>
@@ -10440,13 +10457,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="K294" s="7"/>
       <c r="L294" s="7"/>
@@ -10464,13 +10481,13 @@
       </c>
       <c r="D295" s="7"/>
       <c t="s" r="E295" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F295" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G295" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H295" s="8">
         <v>17</v>
@@ -10497,7 +10514,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10509,10 +10526,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10530,7 +10547,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10563,7 +10580,7 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
@@ -10575,7 +10592,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c t="s" r="J298" s="7">
         <v>180</v>
@@ -10611,7 +10628,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10644,7 +10661,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -10659,7 +10676,7 @@
         <v>158</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10677,7 +10694,7 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
@@ -10689,7 +10706,7 @@
         <v>76</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>133</v>
@@ -10710,7 +10727,7 @@
       </c>
       <c r="D303" s="7"/>
       <c t="s" r="E303" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F303" s="7">
         <v>321</v>
@@ -10725,7 +10742,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J303" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="K303" s="7"/>
       <c r="L303" s="7"/>
@@ -10743,7 +10760,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F304" s="7">
         <v>321</v>
@@ -10752,13 +10769,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -10776,13 +10793,13 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F305" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>60</v>
@@ -10791,7 +10808,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10824,7 +10841,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F307" s="7">
         <v>321</v>
@@ -10836,13 +10853,13 @@
         <v>86</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c t="s" r="K307" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="L307" s="7"/>
       <c t="s" r="M307" s="7">
@@ -10861,7 +10878,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F308" s="7">
         <v>321</v>
@@ -10876,7 +10893,7 @@
         <v>133</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10894,7 +10911,7 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F309" s="7">
         <v>321</v>
@@ -10903,7 +10920,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H309" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="I309" s="7">
         <v>47</v>
@@ -10927,22 +10944,22 @@
       </c>
       <c r="D310" s="7"/>
       <c t="s" r="E310" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F310" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G310" s="8">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c t="s" r="H310" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I310" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c t="s" r="J310" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="K310" s="7"/>
       <c r="L310" s="7"/>
@@ -10975,7 +10992,7 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
@@ -10990,7 +11007,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11008,7 +11025,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11020,10 +11037,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11056,7 +11073,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11065,7 +11082,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I315" s="7">
         <v>99</v>
@@ -11089,19 +11106,19 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>74</v>
@@ -11122,7 +11139,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11155,7 +11172,7 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
@@ -11170,7 +11187,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11188,7 +11205,7 @@
       </c>
       <c r="D319" s="7"/>
       <c t="s" r="E319" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F319" s="7">
         <v>320</v>
@@ -11221,7 +11238,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F320" s="7">
         <v>320</v>
@@ -11233,10 +11250,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="K320" s="7"/>
       <c r="L320" s="7"/>
@@ -11269,7 +11286,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11278,7 +11295,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="I322" s="7">
         <v>194</v>
@@ -11302,13 +11319,13 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>17</v>
@@ -11317,7 +11334,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11335,7 +11352,7 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
@@ -11347,10 +11364,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11368,7 +11385,7 @@
       </c>
       <c r="D325" s="7"/>
       <c t="s" r="E325" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F325" s="7">
         <v>321</v>
@@ -11401,7 +11418,7 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F326" s="7">
         <v>321</v>
@@ -11416,7 +11433,7 @@
         <v>125</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -11434,7 +11451,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F327" s="7">
         <v>321</v>
@@ -11467,7 +11484,7 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F328" s="7">
         <v>321</v>
@@ -11479,7 +11496,7 @@
         <v>86</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c t="s" r="J328" s="7">
         <v>142</v>
@@ -11500,7 +11517,7 @@
       </c>
       <c r="D329" s="7"/>
       <c t="s" r="E329" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F329" s="7">
         <v>321</v>
@@ -11515,7 +11532,7 @@
         <v>180</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11548,7 +11565,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F331" s="7">
         <v>320</v>
@@ -11557,10 +11574,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>74</v>
@@ -11581,13 +11598,13 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F332" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>60</v>
@@ -11614,7 +11631,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F333" s="7">
         <v>320</v>
@@ -11647,7 +11664,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F334" s="7">
         <v>320</v>
@@ -11680,7 +11697,7 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F335" s="7">
         <v>320</v>
@@ -11689,13 +11706,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -11713,22 +11730,22 @@
       </c>
       <c r="D336" s="7"/>
       <c t="s" r="E336" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="F336" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I336" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J336" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="K336" s="7"/>
       <c r="L336" s="7"/>
@@ -11761,7 +11778,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -11794,7 +11811,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -11809,7 +11826,7 @@
         <v>201</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11827,7 +11844,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -11836,13 +11853,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -11860,13 +11877,13 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>17</v>
@@ -11908,7 +11925,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -11920,10 +11937,10 @@
         <v>76</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -11941,7 +11958,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -11974,7 +11991,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -11983,7 +12000,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>199</v>
@@ -12007,13 +12024,13 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>17</v>
@@ -12022,7 +12039,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12055,7 +12072,7 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
@@ -12064,7 +12081,7 @@
         <v>60</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I348" s="7">
         <v>137</v>
@@ -12088,13 +12105,13 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>60</v>
@@ -12121,7 +12138,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12133,7 +12150,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>122</v>
@@ -12154,7 +12171,7 @@
       </c>
       <c r="D351" s="7"/>
       <c t="s" r="E351" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F351" s="7">
         <v>320</v>
@@ -12187,7 +12204,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12202,7 +12219,7 @@
         <v>46</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
@@ -12220,7 +12237,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12235,7 +12252,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12253,7 +12270,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12262,10 +12279,10 @@
         <v>60</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>61</v>
@@ -12301,7 +12318,7 @@
       </c>
       <c r="D356" s="7"/>
       <c t="s" r="E356" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F356" s="7">
         <v>320</v>
@@ -12313,7 +12330,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>28</v>
@@ -12334,7 +12351,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F357" s="7">
         <v>320</v>
@@ -12346,10 +12363,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I357" s="7">
+        <v>333</v>
+      </c>
+      <c t="s" r="J357" s="7">
         <v>332</v>
-      </c>
-      <c t="s" r="J357" s="7">
-        <v>331</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -12367,7 +12384,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F358" s="7">
         <v>320</v>
@@ -12379,7 +12396,7 @@
         <v>82</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>201</v>
@@ -12400,7 +12417,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F359" s="7">
         <v>320</v>
@@ -12433,7 +12450,7 @@
       </c>
       <c r="D360" s="7"/>
       <c t="s" r="E360" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F360" s="7">
         <v>320</v>
@@ -12445,10 +12462,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J360" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K360" s="7"/>
       <c r="L360" s="7"/>
@@ -12466,7 +12483,7 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F361" s="7">
         <v>320</v>
@@ -12478,10 +12495,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -12499,7 +12516,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F362" s="7">
         <v>320</v>
@@ -12508,13 +12525,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>102</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12532,22 +12549,22 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F363" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12580,7 +12597,7 @@
       </c>
       <c r="D365" s="7"/>
       <c t="s" r="E365" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F365" s="7">
         <v>321</v>
@@ -12592,7 +12609,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c t="s" r="J365" s="7">
         <v>146</v>
@@ -12613,7 +12630,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12646,7 +12663,7 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
@@ -12679,7 +12696,7 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
@@ -12694,7 +12711,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12712,7 +12729,7 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
@@ -12727,7 +12744,7 @@
         <v>140</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12745,7 +12762,7 @@
       </c>
       <c r="D370" s="7"/>
       <c t="s" r="E370" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F370" s="7">
         <v>321</v>
@@ -12793,7 +12810,7 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F372" s="7">
         <v>320</v>
@@ -12808,7 +12825,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12826,7 +12843,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F373" s="7">
         <v>320</v>
@@ -12838,7 +12855,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>73</v>
@@ -12859,7 +12876,7 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F374" s="7">
         <v>320</v>
@@ -12871,7 +12888,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>45</v>
@@ -12892,7 +12909,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F375" s="7">
         <v>320</v>
@@ -12907,7 +12924,7 @@
         <v>75</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -12925,7 +12942,7 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F376" s="7">
         <v>320</v>
@@ -12958,7 +12975,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F377" s="7">
         <v>320</v>
@@ -13006,7 +13023,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F379" s="7">
         <v>320</v>
@@ -13018,10 +13035,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13039,7 +13056,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F380" s="7">
         <v>320</v>
@@ -13051,10 +13068,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13072,7 +13089,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F381" s="7">
         <v>320</v>
@@ -13105,7 +13122,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F382" s="7">
         <v>320</v>
@@ -13138,7 +13155,7 @@
       </c>
       <c r="D383" s="7"/>
       <c t="s" r="E383" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F383" s="7">
         <v>320</v>
@@ -13150,10 +13167,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13171,7 +13188,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13204,7 +13221,7 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
@@ -13216,10 +13233,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13252,7 +13269,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F387" s="7">
         <v>321</v>
@@ -13264,10 +13281,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13285,7 +13302,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F388" s="7">
         <v>321</v>
@@ -13318,7 +13335,7 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F389" s="7">
         <v>321</v>
@@ -13333,7 +13350,7 @@
         <v>85</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13351,7 +13368,7 @@
       </c>
       <c r="D390" s="7"/>
       <c t="s" r="E390" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F390" s="7">
         <v>321</v>
@@ -13366,7 +13383,7 @@
         <v>41</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13384,7 +13401,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13396,10 +13413,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13417,7 +13434,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13429,10 +13446,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I392" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13450,7 +13467,7 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
@@ -13483,7 +13500,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13495,10 +13512,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -13531,7 +13548,7 @@
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F396" s="7">
         <v>320</v>
@@ -13546,7 +13563,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13564,7 +13581,7 @@
       </c>
       <c r="D397" s="7"/>
       <c t="s" r="E397" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F397" s="7">
         <v>320</v>
@@ -13579,7 +13596,7 @@
         <v>196</v>
       </c>
       <c t="s" r="J397" s="7">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K397" s="7"/>
       <c r="L397" s="7"/>
@@ -13597,7 +13614,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F398" s="7">
         <v>320</v>
@@ -13606,13 +13623,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H398" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="I398" s="7">
         <v>43</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -13630,22 +13647,22 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F399" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G399" s="8">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c t="s" r="H399" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J399" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
@@ -13663,7 +13680,7 @@
       </c>
       <c r="D400" s="7"/>
       <c t="s" r="E400" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F400" s="7">
         <v>320</v>
@@ -13672,10 +13689,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H400" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="I400" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c t="s" r="J400" s="7">
         <v>193</v>
@@ -13696,22 +13713,22 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F401" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13744,7 +13761,7 @@
       </c>
       <c r="D403" s="7"/>
       <c t="s" r="E403" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F403" s="7">
         <v>320</v>
@@ -13753,13 +13770,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H403" s="8">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="I403" s="7">
         <v>173</v>
       </c>
       <c t="s" r="J403" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K403" s="7"/>
       <c r="L403" s="7"/>
@@ -13777,19 +13794,19 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F404" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>60</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>41</v>
@@ -13810,7 +13827,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F405" s="7">
         <v>320</v>
@@ -13822,10 +13839,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13843,7 +13860,7 @@
       </c>
       <c r="D406" s="7"/>
       <c t="s" r="E406" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F406" s="7">
         <v>320</v>
@@ -13876,7 +13893,7 @@
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F407" s="7">
         <v>320</v>
@@ -13888,10 +13905,10 @@
         <v>119</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
@@ -13909,7 +13926,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F408" s="7">
         <v>320</v>
@@ -13921,7 +13938,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I408" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c t="s" r="J408" s="7">
         <v>109</v>
@@ -13957,7 +13974,7 @@
       </c>
       <c r="D410" s="7"/>
       <c t="s" r="E410" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F410" s="7">
         <v>321</v>
@@ -13972,7 +13989,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J410" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K410" s="7"/>
       <c r="L410" s="7"/>
@@ -13990,7 +14007,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F411" s="7">
         <v>321</v>
@@ -14005,7 +14022,7 @@
         <v>84</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14023,7 +14040,7 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F412" s="7">
         <v>321</v>
@@ -14032,13 +14049,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14056,19 +14073,19 @@
       </c>
       <c r="D413" s="7"/>
       <c t="s" r="E413" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F413" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G413" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H413" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I413" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J413" s="7">
         <v>139</v>
@@ -14089,7 +14106,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F414" s="7">
         <v>321</v>
@@ -14098,13 +14115,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14122,22 +14139,22 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F415" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14170,7 +14187,7 @@
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F417" s="7">
         <v>321</v>
@@ -14182,10 +14199,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14203,7 +14220,7 @@
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F418" s="7">
         <v>321</v>
@@ -14236,7 +14253,7 @@
       </c>
       <c r="D419" s="7"/>
       <c t="s" r="E419" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F419" s="7">
         <v>321</v>
@@ -14248,7 +14265,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I419" s="7">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c t="s" r="J419" s="7">
         <v>140</v>
@@ -14269,7 +14286,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F420" s="7">
         <v>321</v>
@@ -14281,10 +14298,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14317,7 +14334,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F422" s="7">
         <v>320</v>
@@ -14350,7 +14367,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F423" s="7">
         <v>320</v>
@@ -14362,10 +14379,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14383,7 +14400,7 @@
       </c>
       <c r="D424" s="7"/>
       <c t="s" r="E424" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F424" s="7">
         <v>320</v>
@@ -14395,7 +14412,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I424" s="7">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c t="s" r="J424" s="7">
         <v>184</v>
@@ -14416,7 +14433,7 @@
       </c>
       <c r="D425" s="7"/>
       <c t="s" r="E425" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F425" s="7">
         <v>320</v>
@@ -14449,7 +14466,7 @@
       </c>
       <c r="D426" s="7"/>
       <c t="s" r="E426" s="7">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="F426" s="7">
         <v>320</v>
@@ -14461,7 +14478,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I426" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J426" s="7">
         <v>179</v>
@@ -14497,7 +14514,7 @@
       </c>
       <c r="D428" s="7"/>
       <c t="s" r="E428" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F428" s="7">
         <v>320</v>
@@ -14509,10 +14526,10 @@
         <v>96</v>
       </c>
       <c t="s" r="I428" s="7">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c t="s" r="J428" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K428" s="7"/>
       <c r="L428" s="7"/>
@@ -14530,7 +14547,7 @@
       </c>
       <c r="D429" s="7"/>
       <c t="s" r="E429" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F429" s="7">
         <v>320</v>
@@ -14563,7 +14580,7 @@
       </c>
       <c r="D430" s="7"/>
       <c t="s" r="E430" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F430" s="7">
         <v>320</v>
@@ -14596,7 +14613,7 @@
       </c>
       <c r="D431" s="7"/>
       <c t="s" r="E431" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F431" s="7">
         <v>320</v>
@@ -14611,7 +14628,7 @@
         <v>167</v>
       </c>
       <c t="s" r="J431" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K431" s="7"/>
       <c r="L431" s="7"/>
@@ -14629,7 +14646,7 @@
       </c>
       <c r="D432" s="7"/>
       <c t="s" r="E432" s="7">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F432" s="7">
         <v>320</v>
@@ -14641,10 +14658,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I432" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c t="s" r="J432" s="7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K432" s="7"/>
       <c r="L432" s="7"/>
@@ -14677,7 +14694,7 @@
       </c>
       <c r="D434" s="7"/>
       <c t="s" r="E434" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F434" s="7">
         <v>321</v>
@@ -14692,7 +14709,7 @@
         <v>150</v>
       </c>
       <c t="s" r="J434" s="7">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="K434" s="7"/>
       <c r="L434" s="7"/>
@@ -14710,7 +14727,7 @@
       </c>
       <c r="D435" s="7"/>
       <c t="s" r="E435" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F435" s="7">
         <v>321</v>
@@ -14743,7 +14760,7 @@
       </c>
       <c r="D436" s="7"/>
       <c t="s" r="E436" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F436" s="7">
         <v>321</v>
@@ -14776,7 +14793,7 @@
       </c>
       <c r="D437" s="7"/>
       <c t="s" r="E437" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F437" s="7">
         <v>321</v>
@@ -14809,7 +14826,7 @@
       </c>
       <c r="D438" s="7"/>
       <c t="s" r="E438" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F438" s="7">
         <v>321</v>
@@ -14821,7 +14838,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I438" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c t="s" r="J438" s="7">
         <v>65</v>
@@ -14842,7 +14859,7 @@
       </c>
       <c r="D439" s="7"/>
       <c t="s" r="E439" s="7">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F439" s="7">
         <v>321</v>
@@ -14854,10 +14871,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I439" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J439" s="7">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="K439" s="7"/>
       <c r="L439" s="7"/>
@@ -14890,7 +14907,7 @@
       </c>
       <c r="D441" s="7"/>
       <c t="s" r="E441" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F441" s="7">
         <v>321</v>
@@ -14905,7 +14922,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J441" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K441" s="7"/>
       <c r="L441" s="7"/>
@@ -14923,7 +14940,7 @@
       </c>
       <c r="D442" s="7"/>
       <c t="s" r="E442" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F442" s="7">
         <v>321</v>
@@ -14932,10 +14949,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H442" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="I442" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c t="s" r="J442" s="7">
         <v>201</v>
@@ -14956,13 +14973,13 @@
       </c>
       <c r="D443" s="7"/>
       <c t="s" r="E443" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F443" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G443" s="8">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c t="s" r="H443" s="8">
         <v>17</v>
@@ -14971,7 +14988,7 @@
         <v>199</v>
       </c>
       <c t="s" r="J443" s="7">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="K443" s="7"/>
       <c r="L443" s="7"/>
@@ -14989,7 +15006,7 @@
       </c>
       <c r="D444" s="7"/>
       <c t="s" r="E444" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F444" s="7">
         <v>321</v>
@@ -14998,7 +15015,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H444" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="I444" s="7">
         <v>50</v>
@@ -15022,22 +15039,22 @@
       </c>
       <c r="D445" s="7"/>
       <c t="s" r="E445" s="7">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F445" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G445" s="8">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c t="s" r="H445" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I445" s="7">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c t="s" r="J445" s="7">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="K445" s="7"/>
       <c r="L445" s="7"/>
@@ -15070,7 +15087,7 @@
       </c>
       <c r="D447" s="7"/>
       <c t="s" r="E447" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F447" s="7">
         <v>321</v>
@@ -15085,10 +15102,10 @@
         <v>137</v>
       </c>
       <c t="s" r="J447" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="K447" s="7">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="L447" s="7"/>
       <c t="s" r="M447" s="7">
@@ -15107,7 +15124,7 @@
       </c>
       <c r="D448" s="7"/>
       <c t="s" r="E448" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F448" s="7">
         <v>321</v>
@@ -15140,7 +15157,7 @@
       </c>
       <c r="D449" s="7"/>
       <c t="s" r="E449" s="7">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F449" s="7">
         <v>321</v>
@@ -15152,10 +15169,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I449" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J449" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="K449" s="7"/>
       <c r="L449" s="7"/>
@@ -15188,7 +15205,7 @@
       </c>
       <c r="D451" s="7"/>
       <c t="s" r="E451" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F451" s="7">
         <v>321</v>
@@ -15197,7 +15214,7 @@
         <v>17</v>
       </c>
       <c t="s" r="H451" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I451" s="7">
         <v>85</v>
@@ -15221,13 +15238,13 @@
       </c>
       <c r="D452" s="7"/>
       <c t="s" r="E452" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F452" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G452" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H452" s="8">
         <v>26</v>
@@ -15236,7 +15253,7 @@
         <v>62</v>
       </c>
       <c t="s" r="J452" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="K452" s="7"/>
       <c r="L452" s="7"/>
@@ -15254,7 +15271,7 @@
       </c>
       <c r="D453" s="7"/>
       <c t="s" r="E453" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F453" s="7">
         <v>321</v>
@@ -15263,13 +15280,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H453" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="I453" s="7">
         <v>77</v>
       </c>
       <c t="s" r="J453" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="K453" s="7"/>
       <c r="L453" s="7"/>
@@ -15287,22 +15304,22 @@
       </c>
       <c r="D454" s="7"/>
       <c t="s" r="E454" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F454" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G454" s="8">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c t="s" r="H454" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I454" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c t="s" r="J454" s="7">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K454" s="7"/>
       <c r="L454" s="7"/>
@@ -15320,7 +15337,7 @@
       </c>
       <c r="D455" s="7"/>
       <c t="s" r="E455" s="7">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="F455" s="7">
         <v>321</v>
@@ -15335,7 +15352,7 @@
         <v>142</v>
       </c>
       <c t="s" r="J455" s="7">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="K455" s="7"/>
       <c r="L455" s="7"/>
@@ -15368,7 +15385,7 @@
       </c>
       <c r="D457" s="7"/>
       <c t="s" r="E457" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F457" s="7">
         <v>320</v>
@@ -15383,7 +15400,7 @@
         <v>24</v>
       </c>
       <c t="s" r="J457" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K457" s="7"/>
       <c r="L457" s="7"/>
@@ -15401,7 +15418,7 @@
       </c>
       <c r="D458" s="7"/>
       <c t="s" r="E458" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F458" s="7">
         <v>320</v>
@@ -15413,7 +15430,7 @@
         <v>55</v>
       </c>
       <c t="s" r="I458" s="7">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c t="s" r="J458" s="7">
         <v>147</v>
@@ -15434,7 +15451,7 @@
       </c>
       <c r="D459" s="7"/>
       <c t="s" r="E459" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F459" s="7">
         <v>320</v>
@@ -15467,7 +15484,7 @@
       </c>
       <c r="D460" s="7"/>
       <c t="s" r="E460" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F460" s="7">
         <v>320</v>
@@ -15482,7 +15499,7 @@
         <v>141</v>
       </c>
       <c t="s" r="J460" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K460" s="7"/>
       <c r="L460" s="7"/>
@@ -15500,7 +15517,7 @@
       </c>
       <c r="D461" s="7"/>
       <c t="s" r="E461" s="7">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="F461" s="7">
         <v>320</v>
@@ -15512,10 +15529,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I461" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c t="s" r="J461" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K461" s="7"/>
       <c r="L461" s="7"/>
@@ -15548,7 +15565,7 @@
       </c>
       <c r="D463" s="7"/>
       <c t="s" r="E463" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F463" s="7">
         <v>321</v>
@@ -15557,7 +15574,7 @@
         <v>49</v>
       </c>
       <c t="s" r="H463" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I463" s="7">
         <v>105</v>
@@ -15581,13 +15598,13 @@
       </c>
       <c r="D464" s="7"/>
       <c t="s" r="E464" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F464" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G464" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H464" s="8">
         <v>44</v>
@@ -15614,7 +15631,7 @@
       </c>
       <c r="D465" s="7"/>
       <c t="s" r="E465" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F465" s="7">
         <v>321</v>
@@ -15623,13 +15640,13 @@
         <v>44</v>
       </c>
       <c t="s" r="H465" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="I465" s="7">
         <v>106</v>
       </c>
       <c t="s" r="J465" s="7">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="K465" s="7"/>
       <c r="L465" s="7"/>
@@ -15647,13 +15664,13 @@
       </c>
       <c r="D466" s="7"/>
       <c t="s" r="E466" s="7">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F466" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G466" s="8">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c t="s" r="H466" s="8">
         <v>49</v>
@@ -15695,7 +15712,7 @@
       </c>
       <c r="D468" s="7"/>
       <c t="s" r="E468" s="7">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F468" s="7">
         <v>321</v>
@@ -15707,7 +15724,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I468" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c t="s" r="J468" s="7">
         <v>41</v>
@@ -15743,7 +15760,7 @@
       </c>
       <c r="D470" s="7"/>
       <c t="s" r="E470" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F470" s="7">
         <v>321</v>
@@ -15755,10 +15772,10 @@
         <v>82</v>
       </c>
       <c t="s" r="I470" s="7">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c t="s" r="J470" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K470" s="7"/>
       <c r="L470" s="7"/>
@@ -15776,7 +15793,7 @@
       </c>
       <c r="D471" s="7"/>
       <c t="s" r="E471" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F471" s="7">
         <v>321</v>
@@ -15788,7 +15805,7 @@
         <v>60</v>
       </c>
       <c t="s" r="I471" s="7">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c t="s" r="J471" s="7">
         <v>75</v>
@@ -15809,7 +15826,7 @@
       </c>
       <c r="D472" s="7"/>
       <c t="s" r="E472" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F472" s="7">
         <v>321</v>
@@ -15818,13 +15835,13 @@
         <v>60</v>
       </c>
       <c t="s" r="H472" s="8">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c t="s" r="I472" s="7">
         <v>125</v>
       </c>
       <c t="s" r="J472" s="7">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="K472" s="7"/>
       <c r="L472" s="7"/>
@@ -15842,13 +15859,13 @@
       </c>
       <c r="D473" s="7"/>
       <c t="s" r="E473" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F473" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G473" s="8">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c t="s" r="H473" s="8">
         <v>60</v>
@@ -15875,7 +15892,7 @@
       </c>
       <c r="D474" s="7"/>
       <c t="s" r="E474" s="7">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="F474" s="7">
         <v>321</v>
@@ -15923,7 +15940,7 @@
       </c>
       <c r="D476" s="7"/>
       <c t="s" r="E476" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F476" s="7">
         <v>320</v>
@@ -15935,10 +15952,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I476" s="7">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c t="s" r="J476" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="K476" s="7"/>
       <c r="L476" s="7"/>
@@ -15956,7 +15973,7 @@
       </c>
       <c r="D477" s="7"/>
       <c t="s" r="E477" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F477" s="7">
         <v>320</v>
@@ -15968,7 +15985,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I477" s="7">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c t="s" r="J477" s="7">
         <v>39</v>
@@ -15989,7 +16006,7 @@
       </c>
       <c r="D478" s="7"/>
       <c t="s" r="E478" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F478" s="7">
         <v>320</v>
@@ -16022,7 +16039,7 @@
       </c>
       <c r="D479" s="7"/>
       <c t="s" r="E479" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F479" s="7">
         <v>320</v>
@@ -16034,10 +16051,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I479" s="7">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c t="s" r="J479" s="7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K479" s="7"/>
       <c r="L479" s="7"/>
@@ -16055,7 +16072,7 @@
       </c>
       <c r="D480" s="7"/>
       <c t="s" r="E480" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F480" s="7">
         <v>320</v>
@@ -16070,7 +16087,7 @@
         <v>184</v>
       </c>
       <c t="s" r="J480" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K480" s="7"/>
       <c r="L480" s="7"/>
@@ -16088,7 +16105,7 @@
       </c>
       <c r="D481" s="7"/>
       <c t="s" r="E481" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F481" s="7">
         <v>320</v>
@@ -16103,7 +16120,7 @@
         <v>186</v>
       </c>
       <c t="s" r="J481" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K481" s="7"/>
       <c r="L481" s="7"/>
@@ -16121,7 +16138,7 @@
       </c>
       <c r="D482" s="7"/>
       <c t="s" r="E482" s="7">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F482" s="7">
         <v>320</v>
@@ -16133,10 +16150,10 @@
         <v>60</v>
       </c>
       <c t="s" r="I482" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c t="s" r="J482" s="7">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="K482" s="7"/>
       <c r="L482" s="7"/>
@@ -16169,7 +16186,7 @@
       </c>
       <c r="D484" s="7"/>
       <c t="s" r="E484" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F484" s="7">
         <v>330</v>
@@ -16181,10 +16198,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I484" s="7">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c t="s" r="J484" s="7">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="K484" s="7"/>
       <c r="L484" s="7"/>
@@ -16202,7 +16219,7 @@
       </c>
       <c r="D485" s="7"/>
       <c t="s" r="E485" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F485" s="7">
         <v>330</v>
@@ -16211,13 +16228,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H485" s="8">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c t="s" r="I485" s="7">
         <v>153</v>
       </c>
       <c t="s" r="J485" s="7">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K485" s="7"/>
       <c r="L485" s="7"/>
@@ -16235,13 +16252,13 @@
       </c>
       <c r="D486" s="7"/>
       <c t="s" r="E486" s="7">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F486" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G486" s="8">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c t="s" r="H486" s="8">
         <v>49</v>
@@ -16283,19 +16300,19 @@
       </c>
       <c r="D488" s="7"/>
       <c t="s" r="E488" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F488" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G488" s="8">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c t="s" r="H488" s="8">
         <v>82</v>
       </c>
       <c t="s" r="I488" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J488" s="7">
         <v>75</v>
@@ -16316,7 +16333,7 @@
       </c>
       <c r="D489" s="7"/>
       <c t="s" r="E489" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F489" s="7">
         <v>330</v>
@@ -16328,7 +16345,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I489" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c t="s" r="J489" s="7">
         <v>190</v>
@@ -16349,7 +16366,7 @@
       </c>
       <c r="D490" s="7"/>
       <c t="s" r="E490" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F490" s="7">
         <v>330</v>
@@ -16358,13 +16375,13 @@
         <v>49</v>
       </c>
       <c t="s" r="H490" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="I490" s="7">
         <v>91</v>
       </c>
       <c t="s" r="J490" s="7">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="K490" s="7"/>
       <c r="L490" s="7"/>
@@ -16382,19 +16399,19 @@
       </c>
       <c r="D491" s="7"/>
       <c t="s" r="E491" s="7">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F491" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G491" s="8">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c t="s" r="H491" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I491" s="7">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c t="s" r="J491" s="7">
         <v>196</v>
@@ -16426,11 +16443,11 @@
         <v>35</v>
       </c>
       <c t="s" r="C493" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D493" s="7"/>
       <c t="s" r="E493" s="7">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F493" s="7">
         <v>330</v>
@@ -16439,13 +16456,13 @@
         <v>82</v>
       </c>
       <c t="s" r="H493" s="8">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c t="s" r="I493" s="7">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c t="s" r="J493" s="7">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="K493" s="7"/>
       <c r="L493" s="7"/>
@@ -16478,22 +16495,22 @@
       </c>
       <c r="D495" s="7"/>
       <c t="s" r="E495" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F495" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G495" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c t="s" r="H495" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I495" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J495" s="7">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="K495" s="7"/>
       <c r="L495" s="7"/>
@@ -16511,7 +16528,7 @@
       </c>
       <c r="D496" s="7"/>
       <c t="s" r="E496" s="7">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F496" s="7">
         <v>330</v>
@@ -16520,13 +16537,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H496" s="8">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c t="s" r="I496" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J496" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="K496" s="7"/>
       <c r="L496" s="7"/>
@@ -16559,7 +16576,7 @@
       </c>
       <c r="D498" s="7"/>
       <c t="s" r="E498" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F498" s="7">
         <v>330</v>
@@ -16568,10 +16585,10 @@
         <v>49</v>
       </c>
       <c t="s" r="H498" s="8">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c t="s" r="I498" s="7">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c t="s" r="J498" s="7">
         <v>185</v>
@@ -16592,22 +16609,22 @@
       </c>
       <c r="D499" s="7"/>
       <c t="s" r="E499" s="7">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="F499" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G499" s="8">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c t="s" r="H499" s="8">
         <v>49</v>
       </c>
       <c t="s" r="I499" s="7">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c t="s" r="J499" s="7">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="K499" s="7"/>
       <c r="L499" s="7"/>
@@ -16640,7 +16657,7 @@
       </c>
       <c r="D501" s="7"/>
       <c t="s" r="E501" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F501" s="7">
         <v>330</v>
@@ -16649,10 +16666,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H501" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="I501" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J501" s="7">
         <v>109</v>
@@ -16673,22 +16690,22 @@
       </c>
       <c r="D502" s="7"/>
       <c t="s" r="E502" s="7">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F502" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G502" s="8">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c t="s" r="H502" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I502" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J502" s="7">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K502" s="7"/>
       <c r="L502" s="7"/>
@@ -16696,7 +16713,7 @@
     </row>
     <row r="503" ht="15.75" customHeight="1">
       <c t="s" r="A503" s="9">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B503" s="9"/>
       <c r="C503" s="9"/>
@@ -16716,7 +16733,7 @@
     <row r="504" ht="65.25" customHeight="1"/>
     <row r="505" ht="17.25" customHeight="1">
       <c t="s" r="A505" s="10">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B505" s="10"/>
       <c r="C505" s="10"/>
@@ -16729,7 +16746,7 @@
       <c r="J505" s="10"/>
       <c r="K505" s="10"/>
       <c t="s" r="L505" s="11">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M505" s="11"/>
       <c r="N505" s="11"/>
